--- a/StructureDefinition-ncpi-study-family.xlsx
+++ b/StructureDefinition-ncpi-study-family.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -693,7 +693,7 @@
     <t>Group.managingEntity</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|RelatedPerson|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -943,7 +943,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1327,7 +1327,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.62109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1342,7 +1342,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="75.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="35.6953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="38.78125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-study-family.xlsx
+++ b/StructureDefinition-ncpi-study-family.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="321">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -470,6 +470,9 @@
     <t>Free text describing the study family, such as potential inheritance or details about consanguinity</t>
   </si>
   <si>
+    <t>Free text describing containing resource.</t>
+  </si>
+  <si>
     <t>Group.extension:consanguinity</t>
   </si>
   <si>
@@ -483,7 +486,7 @@
     <t>Is there known or suspected consanguinity in this study family?</t>
   </si>
   <si>
-    <t>Extension containing Consanguinity</t>
+    <t>Extension containing a consanguinity assertion</t>
   </si>
   <si>
     <t>Group.extension:studyFamilyFocus</t>
@@ -499,7 +502,7 @@
     <t>What is this study family investigating? EG, a specific condition</t>
   </si>
   <si>
-    <t>Extension containing Study Family Focus</t>
+    <t>Extension containing a study family focus assertion</t>
   </si>
   <si>
     <t>Group.modifierExtension</t>
@@ -874,7 +877,7 @@
 </t>
   </si>
   <si>
-    <t>The participant we are describing.</t>
+    <t>The participant described by this member.</t>
   </si>
   <si>
     <t>A reference to the entity that is a member of the group. Must be consistent with Group.type. If the entity is another group, then the type must be the same.</t>
@@ -2474,7 +2477,7 @@
         <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2548,13 +2551,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -2576,13 +2579,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2656,13 +2659,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>128</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -2684,13 +2687,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2764,14 +2767,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2793,16 +2796,16 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2851,7 +2854,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2874,10 +2877,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2900,17 +2903,17 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -2959,7 +2962,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2974,18 +2977,18 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3008,23 +3011,23 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="R16" t="s" s="2">
         <v>20</v>
@@ -3069,7 +3072,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3084,18 +3087,18 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3121,16 +3124,16 @@
         <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3155,13 +3158,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3179,7 +3182,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>84</v>
@@ -3194,18 +3197,18 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3228,17 +3231,17 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3287,7 +3290,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>84</v>
@@ -3296,24 +3299,24 @@
         <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3336,16 +3339,16 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3371,10 +3374,10 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>20</v>
@@ -3395,7 +3398,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3410,18 +3413,18 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3444,17 +3447,17 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3503,7 +3506,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3518,7 +3521,7 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
@@ -3526,10 +3529,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3552,19 +3555,19 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3613,7 +3616,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3628,7 +3631,7 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
@@ -3636,10 +3639,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3662,16 +3665,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3721,7 +3724,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3744,10 +3747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3770,19 +3773,19 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -3831,7 +3834,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3846,7 +3849,7 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
@@ -3854,10 +3857,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3880,13 +3883,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3937,7 +3940,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3952,7 +3955,7 @@
         <v>20</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
@@ -3960,14 +3963,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3989,13 +3992,13 @@
         <v>129</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4045,7 +4048,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4060,7 +4063,7 @@
         <v>135</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
@@ -4068,14 +4071,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4097,16 +4100,16 @@
         <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4155,7 +4158,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4178,10 +4181,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4204,17 +4207,17 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4239,10 +4242,10 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>20</v>
@@ -4263,7 +4266,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -4278,7 +4281,7 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
@@ -4286,10 +4289,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4312,19 +4315,19 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4349,10 +4352,10 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>20</v>
@@ -4373,7 +4376,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4388,7 +4391,7 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
@@ -4396,10 +4399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4422,19 +4425,19 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4483,7 +4486,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>84</v>
@@ -4498,7 +4501,7 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
@@ -4506,10 +4509,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4532,13 +4535,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4589,7 +4592,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4612,10 +4615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4638,17 +4641,17 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -4697,7 +4700,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4706,13 +4709,13 @@
         <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
@@ -4720,10 +4723,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4746,13 +4749,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4803,7 +4806,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4818,7 +4821,7 @@
         <v>20</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
@@ -4826,14 +4829,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4855,13 +4858,13 @@
         <v>129</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4911,7 +4914,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4926,7 +4929,7 @@
         <v>135</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
@@ -4934,14 +4937,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4963,16 +4966,16 @@
         <v>129</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5021,7 +5024,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5044,10 +5047,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5070,13 +5073,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5127,7 +5130,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -5150,10 +5153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5176,13 +5179,13 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5233,7 +5236,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5248,7 +5251,7 @@
         <v>20</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -5256,14 +5259,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5285,13 +5288,13 @@
         <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5332,7 +5335,7 @@
         <v>132</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>20</v>
@@ -5341,7 +5344,7 @@
         <v>133</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -5356,7 +5359,7 @@
         <v>135</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -5364,13 +5367,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
@@ -5392,13 +5395,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5449,7 +5452,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5472,10 +5475,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5498,16 +5501,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5557,7 +5560,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -5566,7 +5569,7 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>96</v>
@@ -5580,10 +5583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5609,13 +5612,13 @@
         <v>98</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5641,13 +5644,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -5665,7 +5668,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5688,10 +5691,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5714,16 +5717,16 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5773,7 +5776,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5788,7 +5791,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -5796,10 +5799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5822,16 +5825,16 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5881,7 +5884,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -5904,10 +5907,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5930,23 +5933,23 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="R43" t="s" s="2">
         <v>20</v>
@@ -5991,7 +5994,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6014,10 +6017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6040,23 +6043,23 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="R44" t="s" s="2">
         <v>20</v>
@@ -6101,7 +6104,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>

--- a/StructureDefinition-ncpi-study-family.xlsx
+++ b/StructureDefinition-ncpi-study-family.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,7 +486,7 @@
     <t>Is there known or suspected consanguinity in this study family?</t>
   </si>
   <si>
-    <t>Extension containing a consanguinity assertion</t>
+    <t>Extension containing Consanguinity</t>
   </si>
   <si>
     <t>Group.extension:studyFamilyFocus</t>
@@ -502,7 +502,7 @@
     <t>What is this study family investigating? EG, a specific condition</t>
   </si>
   <si>
-    <t>Extension containing a study family focus assertion</t>
+    <t>Extension containing Study Family Focus</t>
   </si>
   <si>
     <t>Group.modifierExtension</t>
@@ -877,7 +877,7 @@
 </t>
   </si>
   <si>
-    <t>The participant described by this member.</t>
+    <t>The participant we are describing.</t>
   </si>
   <si>
     <t>A reference to the entity that is a member of the group. Must be consistent with Group.type. If the entity is another group, then the type must be the same.</t>

--- a/StructureDefinition-ncpi-study-family.xlsx
+++ b/StructureDefinition-ncpi-study-family.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-study-family.xlsx
+++ b/StructureDefinition-ncpi-study-family.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -486,7 +486,7 @@
     <t>Is there known or suspected consanguinity in this study family?</t>
   </si>
   <si>
-    <t>Extension containing Consanguinity</t>
+    <t>Extension containing a consanguinity assertion</t>
   </si>
   <si>
     <t>Group.extension:studyFamilyFocus</t>
@@ -502,7 +502,7 @@
     <t>What is this study family investigating? EG, a specific condition</t>
   </si>
   <si>
-    <t>Extension containing Study Family Focus</t>
+    <t>Extension containing a study family focus assertion</t>
   </si>
   <si>
     <t>Group.modifierExtension</t>
@@ -877,7 +877,7 @@
 </t>
   </si>
   <si>
-    <t>The participant we are describing.</t>
+    <t>The participant described by this member.</t>
   </si>
   <si>
     <t>A reference to the entity that is a member of the group. Must be consistent with Group.type. If the entity is another group, then the type must be the same.</t>
